--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/49.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/49.xlsx
@@ -426,13 +426,13 @@
         <v>-9.666001820333717</v>
       </c>
       <c r="E2">
-        <v>-22.17438602568471</v>
+        <v>-34.87769301131965</v>
       </c>
       <c r="F2">
-        <v>-5.496352888708884</v>
+        <v>-6.567532172984383</v>
       </c>
       <c r="G2">
-        <v>-15.17054463419593</v>
+        <v>-21.43309038865307</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.379193097786633</v>
       </c>
       <c r="E3">
-        <v>-23.0364625655769</v>
+        <v>-35.52257488085596</v>
       </c>
       <c r="F3">
-        <v>-5.348920058358628</v>
+        <v>-6.745290705583726</v>
       </c>
       <c r="G3">
-        <v>-15.17523236667953</v>
+        <v>-21.99605031287891</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.02193076748582</v>
       </c>
       <c r="E4">
-        <v>-22.47809266348313</v>
+        <v>-35.99506680186827</v>
       </c>
       <c r="F4">
-        <v>-5.393707398725788</v>
+        <v>-6.819441185277921</v>
       </c>
       <c r="G4">
-        <v>-14.48655613087264</v>
+        <v>-21.54047952012872</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.611131510787692</v>
       </c>
       <c r="E5">
-        <v>-23.2458727891136</v>
+        <v>-36.27713865509504</v>
       </c>
       <c r="F5">
-        <v>-5.252072311827726</v>
+        <v>-6.822283313836927</v>
       </c>
       <c r="G5">
-        <v>-15.1217455376743</v>
+        <v>-21.86357221203389</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.154923102608757</v>
       </c>
       <c r="E6">
-        <v>-23.50486527456028</v>
+        <v>-36.29025538005826</v>
       </c>
       <c r="F6">
-        <v>-5.115768597534082</v>
+        <v>-6.821174958251981</v>
       </c>
       <c r="G6">
-        <v>-14.0682703572585</v>
+        <v>-22.03163040106222</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.665942239056873</v>
       </c>
       <c r="E7">
-        <v>-25.06204898920785</v>
+        <v>-36.85689201145303</v>
       </c>
       <c r="F7">
-        <v>-5.128928870462357</v>
+        <v>-6.616729741404049</v>
       </c>
       <c r="G7">
-        <v>-14.23916899435953</v>
+        <v>-21.73006618679893</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.151442378612045</v>
       </c>
       <c r="E8">
-        <v>-24.17852559641534</v>
+        <v>-37.61504233710619</v>
       </c>
       <c r="F8">
-        <v>-5.220175196615529</v>
+        <v>-6.569062167577354</v>
       </c>
       <c r="G8">
-        <v>-14.59585544712445</v>
+        <v>-21.23063232092617</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.620096851919559</v>
       </c>
       <c r="E9">
-        <v>-25.14049574444273</v>
+        <v>-37.65117050273938</v>
       </c>
       <c r="F9">
-        <v>-5.289488010677374</v>
+        <v>-6.43403413908402</v>
       </c>
       <c r="G9">
-        <v>-14.16186279019924</v>
+        <v>-21.10788225814831</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.078738497702717</v>
       </c>
       <c r="E10">
-        <v>-25.05611668825781</v>
+        <v>-37.33273953170502</v>
       </c>
       <c r="F10">
-        <v>-4.962920729471725</v>
+        <v>-6.476599798076873</v>
       </c>
       <c r="G10">
-        <v>-14.56640648927987</v>
+        <v>-21.50747007055665</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.533526833499356</v>
       </c>
       <c r="E11">
-        <v>-25.71452058118101</v>
+        <v>-38.41278963948242</v>
       </c>
       <c r="F11">
-        <v>-4.887410070502134</v>
+        <v>-6.340277859700367</v>
       </c>
       <c r="G11">
-        <v>-14.1868209930198</v>
+        <v>-21.38193418370749</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.989728868923637</v>
       </c>
       <c r="E12">
-        <v>-25.49612133673909</v>
+        <v>-38.51889404971914</v>
       </c>
       <c r="F12">
-        <v>-4.823289463321035</v>
+        <v>-6.418307583941872</v>
       </c>
       <c r="G12">
-        <v>-13.68493897872075</v>
+        <v>-21.14860362355411</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.450601588163664</v>
       </c>
       <c r="E13">
-        <v>-26.59570728138557</v>
+        <v>-38.69290066346387</v>
       </c>
       <c r="F13">
-        <v>-4.763286670499253</v>
+        <v>-6.293484213483626</v>
       </c>
       <c r="G13">
-        <v>-13.21759257548737</v>
+        <v>-21.06726683019976</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.927676753949291</v>
       </c>
       <c r="E14">
-        <v>-27.28837360865082</v>
+        <v>-39.13444499310776</v>
       </c>
       <c r="F14">
-        <v>-4.316855454475919</v>
+        <v>-6.219227702761873</v>
       </c>
       <c r="G14">
-        <v>-13.14843196862646</v>
+        <v>-20.38988617577286</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.429397259766026</v>
       </c>
       <c r="E15">
-        <v>-27.63726083162376</v>
+        <v>-40.15431394556023</v>
       </c>
       <c r="F15">
-        <v>-4.529803862713587</v>
+        <v>-6.054597965129498</v>
       </c>
       <c r="G15">
-        <v>-12.9794650348476</v>
+        <v>-20.28757211060892</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.963726767563994</v>
       </c>
       <c r="E16">
-        <v>-28.01022595089549</v>
+        <v>-39.99954202516307</v>
       </c>
       <c r="F16">
-        <v>-4.315185465791874</v>
+        <v>-5.917764924065465</v>
       </c>
       <c r="G16">
-        <v>-12.57918366314878</v>
+        <v>-20.35657712182948</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.53810387408664</v>
       </c>
       <c r="E17">
-        <v>-28.38780558518104</v>
+        <v>-39.92707285561832</v>
       </c>
       <c r="F17">
-        <v>-3.950424648745348</v>
+        <v>-6.130205543085218</v>
       </c>
       <c r="G17">
-        <v>-12.3017135993203</v>
+        <v>-20.54085367345471</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.158216799399022</v>
       </c>
       <c r="E18">
-        <v>-29.12715595099136</v>
+        <v>-40.68235892146163</v>
       </c>
       <c r="F18">
-        <v>-3.80430478072853</v>
+        <v>-5.580977245844076</v>
       </c>
       <c r="G18">
-        <v>-12.15390436208293</v>
+        <v>-19.88193096568202</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.827666862955057</v>
       </c>
       <c r="E19">
-        <v>-29.68246460465594</v>
+        <v>-41.18131071610076</v>
       </c>
       <c r="F19">
-        <v>-3.825535837262281</v>
+        <v>-5.457540562418115</v>
       </c>
       <c r="G19">
-        <v>-12.25064843437705</v>
+        <v>-19.97122465524001</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.547639427009975</v>
       </c>
       <c r="E20">
-        <v>-29.7867598895266</v>
+        <v>-41.80542726807489</v>
       </c>
       <c r="F20">
-        <v>-3.615094897152886</v>
+        <v>-5.628585177217769</v>
       </c>
       <c r="G20">
-        <v>-12.14800165938641</v>
+        <v>-20.05195892930622</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.317861514572831</v>
       </c>
       <c r="E21">
-        <v>-31.10696403087877</v>
+        <v>-41.94156225369348</v>
       </c>
       <c r="F21">
-        <v>-3.305030351345809</v>
+        <v>-5.546591714953868</v>
       </c>
       <c r="G21">
-        <v>-12.04463649601374</v>
+        <v>-19.89109455573472</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.139926283650589</v>
       </c>
       <c r="E22">
-        <v>-30.89865422652593</v>
+        <v>-42.4795993074928</v>
       </c>
       <c r="F22">
-        <v>-3.502630768344408</v>
+        <v>-5.321926049803601</v>
       </c>
       <c r="G22">
-        <v>-11.99881192465915</v>
+        <v>-19.58960317347329</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.012874524662241</v>
       </c>
       <c r="E23">
-        <v>-31.60124696881599</v>
+        <v>-42.01214531381403</v>
       </c>
       <c r="F23">
-        <v>-3.085718424719834</v>
+        <v>-5.230687178957054</v>
       </c>
       <c r="G23">
-        <v>-11.92395055837961</v>
+        <v>-19.49050530330075</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.9345688241030118</v>
       </c>
       <c r="E24">
-        <v>-31.13465112096166</v>
+        <v>-42.39754109423681</v>
       </c>
       <c r="F24">
-        <v>-3.22617391643631</v>
+        <v>-4.840715828373728</v>
       </c>
       <c r="G24">
-        <v>-12.27254438257379</v>
+        <v>-19.57214335629918</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.9037318627560977</v>
       </c>
       <c r="E25">
-        <v>-32.37535337263517</v>
+        <v>-42.5138368352278</v>
       </c>
       <c r="F25">
-        <v>-3.122489653730104</v>
+        <v>-4.969852507898351</v>
       </c>
       <c r="G25">
-        <v>-12.34500891388289</v>
+        <v>-20.01634573566751</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.9180021279420506</v>
       </c>
       <c r="E26">
-        <v>-31.22337298371994</v>
+        <v>-43.05368980710421</v>
       </c>
       <c r="F26">
-        <v>-2.93025540076684</v>
+        <v>-5.118774742838841</v>
       </c>
       <c r="G26">
-        <v>-12.23044417495088</v>
+        <v>-19.92575596753089</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.9741079210803749</v>
       </c>
       <c r="E27">
-        <v>-31.39043744681092</v>
+        <v>-42.15459752067332</v>
       </c>
       <c r="F27">
-        <v>-3.012133719961751</v>
+        <v>-5.283570153951775</v>
       </c>
       <c r="G27">
-        <v>-12.07381564439688</v>
+        <v>-19.81752264694273</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.067098479822834</v>
       </c>
       <c r="E28">
-        <v>-31.8713568579515</v>
+        <v>-41.64214181654332</v>
       </c>
       <c r="F28">
-        <v>-2.646378033664463</v>
+        <v>-5.177200324125693</v>
       </c>
       <c r="G28">
-        <v>-12.11356867523244</v>
+        <v>-20.31535586404725</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.191870294501675</v>
       </c>
       <c r="E29">
-        <v>-32.43708100183373</v>
+        <v>-42.88398977214077</v>
       </c>
       <c r="F29">
-        <v>-3.093161305833988</v>
+        <v>-5.068979093154354</v>
       </c>
       <c r="G29">
-        <v>-12.47496106848144</v>
+        <v>-19.41093965180991</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.342997830080166</v>
       </c>
       <c r="E30">
-        <v>-31.44244470655201</v>
+        <v>-42.45200957960108</v>
       </c>
       <c r="F30">
-        <v>-3.277817653796442</v>
+        <v>-5.085980505729411</v>
       </c>
       <c r="G30">
-        <v>-12.27656007431292</v>
+        <v>-20.2565274698144</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.513877884977711</v>
       </c>
       <c r="E31">
-        <v>-31.03662777259163</v>
+        <v>-42.0328494969771</v>
       </c>
       <c r="F31">
-        <v>-2.924671376104568</v>
+        <v>-5.092041670015695</v>
       </c>
       <c r="G31">
-        <v>-12.09349352708231</v>
+        <v>-20.63016557101317</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.697093010719057</v>
       </c>
       <c r="E32">
-        <v>-30.96492844362819</v>
+        <v>-41.65819978537451</v>
       </c>
       <c r="F32">
-        <v>-2.945640668539035</v>
+        <v>-5.204112324307843</v>
       </c>
       <c r="G32">
-        <v>-12.67269664299657</v>
+        <v>-20.19039766739469</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.887325409600381</v>
       </c>
       <c r="E33">
-        <v>-30.34079151352102</v>
+        <v>-42.0124804208906</v>
       </c>
       <c r="F33">
-        <v>-2.809491030582311</v>
+        <v>-5.169597568102799</v>
       </c>
       <c r="G33">
-        <v>-12.43152671100621</v>
+        <v>-20.34229708364584</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.078864383389505</v>
       </c>
       <c r="E34">
-        <v>-30.03304094843375</v>
+        <v>-41.29553241599623</v>
       </c>
       <c r="F34">
-        <v>-2.899779764017846</v>
+        <v>-5.429159866830802</v>
       </c>
       <c r="G34">
-        <v>-12.86714815633675</v>
+        <v>-20.24351702584507</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.266634789480929</v>
       </c>
       <c r="E35">
-        <v>-29.97305678172815</v>
+        <v>-41.20108656209226</v>
       </c>
       <c r="F35">
-        <v>-3.060063886255133</v>
+        <v>-4.996673387666194</v>
       </c>
       <c r="G35">
-        <v>-12.69752242399557</v>
+        <v>-20.59993863496685</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.446021125101291</v>
       </c>
       <c r="E36">
-        <v>-30.01194505226902</v>
+        <v>-41.94290494623675</v>
       </c>
       <c r="F36">
-        <v>-3.121877490219435</v>
+        <v>-5.09249561535243</v>
       </c>
       <c r="G36">
-        <v>-12.24985721399316</v>
+        <v>-20.74072123929713</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.613592803440437</v>
       </c>
       <c r="E37">
-        <v>-30.00421268290092</v>
+        <v>-41.35387048240004</v>
       </c>
       <c r="F37">
-        <v>-3.240739928847137</v>
+        <v>-5.441397338472359</v>
       </c>
       <c r="G37">
-        <v>-12.1458266309671</v>
+        <v>-20.26046536373336</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.766657000294324</v>
       </c>
       <c r="E38">
-        <v>-28.99839784953127</v>
+        <v>-40.63944483752794</v>
       </c>
       <c r="F38">
-        <v>-2.819137368987911</v>
+        <v>-5.156548296406498</v>
       </c>
       <c r="G38">
-        <v>-12.28164838280678</v>
+        <v>-20.56923166981734</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.902441081255931</v>
       </c>
       <c r="E39">
-        <v>-28.90209532128415</v>
+        <v>-40.49125278986394</v>
       </c>
       <c r="F39">
-        <v>-3.07885540078764</v>
+        <v>-5.303238909563846</v>
       </c>
       <c r="G39">
-        <v>-11.97696232409996</v>
+        <v>-20.05388235626453</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.019116647588873</v>
       </c>
       <c r="E40">
-        <v>-29.16504569301354</v>
+        <v>-40.15422790455408</v>
       </c>
       <c r="F40">
-        <v>-3.189911305011359</v>
+        <v>-5.184407948897451</v>
       </c>
       <c r="G40">
-        <v>-11.99899069411827</v>
+        <v>-20.07406013132639</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.116325787773385</v>
       </c>
       <c r="E41">
-        <v>-28.94549621617366</v>
+        <v>-39.01924514282664</v>
       </c>
       <c r="F41">
-        <v>-3.115059198126993</v>
+        <v>-5.330921291430601</v>
       </c>
       <c r="G41">
-        <v>-12.19067128084207</v>
+        <v>-20.40257218627935</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.19365007633338</v>
       </c>
       <c r="E42">
-        <v>-27.86388378486362</v>
+        <v>-39.36131248394403</v>
       </c>
       <c r="F42">
-        <v>-3.085656297164624</v>
+        <v>-5.272986932013608</v>
       </c>
       <c r="G42">
-        <v>-12.64246474113195</v>
+        <v>-19.32908475807866</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.250839192234504</v>
       </c>
       <c r="E43">
-        <v>-27.69072852423233</v>
+        <v>-39.37125474862788</v>
       </c>
       <c r="F43">
-        <v>-3.21206847630144</v>
+        <v>-5.244713095821256</v>
       </c>
       <c r="G43">
-        <v>-12.24024007920158</v>
+        <v>-19.82465356203432</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.287086466859225</v>
       </c>
       <c r="E44">
-        <v>-27.30860683051709</v>
+        <v>-38.94141878853082</v>
       </c>
       <c r="F44">
-        <v>-3.201035450863553</v>
+        <v>-5.326366927450009</v>
       </c>
       <c r="G44">
-        <v>-12.32840983854899</v>
+        <v>-20.32134464092779</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.303524445961296</v>
       </c>
       <c r="E45">
-        <v>-27.32875853985122</v>
+        <v>-38.5612624525349</v>
       </c>
       <c r="F45">
-        <v>-3.257742998156999</v>
+        <v>-5.490169954414388</v>
       </c>
       <c r="G45">
-        <v>-12.20362544553724</v>
+        <v>-20.56580194463865</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.301473160485058</v>
       </c>
       <c r="E46">
-        <v>-26.54437702850863</v>
+        <v>-39.31182531998822</v>
       </c>
       <c r="F46">
-        <v>-3.38086324523509</v>
+        <v>-5.244825753788036</v>
       </c>
       <c r="G46">
-        <v>-12.03260597352403</v>
+        <v>-20.66653687958037</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.282706020074312</v>
       </c>
       <c r="E47">
-        <v>-26.88576057005087</v>
+        <v>-38.4117141269056</v>
       </c>
       <c r="F47">
-        <v>-3.332905742817415</v>
+        <v>-5.212840831631142</v>
       </c>
       <c r="G47">
-        <v>-11.76792454711376</v>
+        <v>-20.0223974129133</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.250707170143186</v>
       </c>
       <c r="E48">
-        <v>-25.76309752186129</v>
+        <v>-39.1714199833804</v>
       </c>
       <c r="F48">
-        <v>-3.367979647019349</v>
+        <v>-5.576927357611789</v>
       </c>
       <c r="G48">
-        <v>-11.93940087441139</v>
+        <v>-20.04038526210093</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.209941225675363</v>
       </c>
       <c r="E49">
-        <v>-25.64696480593459</v>
+        <v>-38.18670104617547</v>
       </c>
       <c r="F49">
-        <v>-3.492689531143412</v>
+        <v>-5.520749965456135</v>
       </c>
       <c r="G49">
-        <v>-11.95922442110054</v>
+        <v>-20.2909803172416</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.164508218716103</v>
       </c>
       <c r="E50">
-        <v>-25.72588252246626</v>
+        <v>-37.20243269213431</v>
       </c>
       <c r="F50">
-        <v>-3.579783251506349</v>
+        <v>-5.46674123916101</v>
       </c>
       <c r="G50">
-        <v>-11.70132630250024</v>
+        <v>-19.66304266044372</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.117827417983789</v>
       </c>
       <c r="E51">
-        <v>-25.2796919784905</v>
+        <v>-37.37040058578982</v>
       </c>
       <c r="F51">
-        <v>-3.68636597175495</v>
+        <v>-5.507964942961327</v>
       </c>
       <c r="G51">
-        <v>-12.62323047154878</v>
+        <v>-20.16616943986553</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.072480631817223</v>
       </c>
       <c r="E52">
-        <v>-25.5951364209168</v>
+        <v>-37.3833791922958</v>
       </c>
       <c r="F52">
-        <v>-3.55255812844594</v>
+        <v>-5.362497828457914</v>
       </c>
       <c r="G52">
-        <v>-11.77053656754424</v>
+        <v>-20.56204282017881</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.031751532120353</v>
       </c>
       <c r="E53">
-        <v>-25.40552015726763</v>
+        <v>-36.28374117019823</v>
       </c>
       <c r="F53">
-        <v>-3.430891666159763</v>
+        <v>-5.291457039993829</v>
       </c>
       <c r="G53">
-        <v>-12.29279167909197</v>
+        <v>-20.60818685917794</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.996886530446976</v>
       </c>
       <c r="E54">
-        <v>-25.06592989143243</v>
+        <v>-36.41376724438047</v>
       </c>
       <c r="F54">
-        <v>-3.682224963108355</v>
+        <v>-5.355690305141708</v>
       </c>
       <c r="G54">
-        <v>-12.25212162714202</v>
+        <v>-20.50350409868065</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.966815138998205</v>
       </c>
       <c r="E55">
-        <v>-24.12437863270562</v>
+        <v>-37.33473658874241</v>
       </c>
       <c r="F55">
-        <v>-3.672398040608945</v>
+        <v>-5.553792712786405</v>
       </c>
       <c r="G55">
-        <v>-12.575661242695</v>
+        <v>-20.83435339878433</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.940880504015541</v>
       </c>
       <c r="E56">
-        <v>-23.76301093536754</v>
+        <v>-35.63675582448536</v>
       </c>
       <c r="F56">
-        <v>-3.720283475062576</v>
+        <v>-5.508817333018808</v>
       </c>
       <c r="G56">
-        <v>-12.2945727525921</v>
+        <v>-20.2688691835848</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.917349558435425</v>
       </c>
       <c r="E57">
-        <v>-22.70548545730429</v>
+        <v>-36.35274605712711</v>
       </c>
       <c r="F57">
-        <v>-3.380299127033783</v>
+        <v>-5.387197259307188</v>
       </c>
       <c r="G57">
-        <v>-12.48125772609714</v>
+        <v>-20.2419014796219</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.893851955575249</v>
       </c>
       <c r="E58">
-        <v>-23.14141900765268</v>
+        <v>-35.69128318001172</v>
       </c>
       <c r="F58">
-        <v>-3.754707939220715</v>
+        <v>-5.506635413279835</v>
       </c>
       <c r="G58">
-        <v>-11.96935137990518</v>
+        <v>-19.95331956969086</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.867905468858472</v>
       </c>
       <c r="E59">
-        <v>-23.82145089243652</v>
+        <v>-35.65028237634627</v>
       </c>
       <c r="F59">
-        <v>-3.648291720820076</v>
+        <v>-5.652723803335347</v>
       </c>
       <c r="G59">
-        <v>-12.2411604108615</v>
+        <v>-19.95706214142301</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.837812511027483</v>
       </c>
       <c r="E60">
-        <v>-22.79427977564669</v>
+        <v>-35.44684973849969</v>
       </c>
       <c r="F60">
-        <v>-3.840130014164802</v>
+        <v>-5.480220433539364</v>
       </c>
       <c r="G60">
-        <v>-12.64910900602927</v>
+        <v>-20.92366860688833</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.803418507473148</v>
       </c>
       <c r="E61">
-        <v>-23.5227618038386</v>
+        <v>-35.94858880889054</v>
       </c>
       <c r="F61">
-        <v>-3.95504114028115</v>
+        <v>-5.571851122167433</v>
       </c>
       <c r="G61">
-        <v>-12.46115609358268</v>
+        <v>-20.08433937522583</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.76434978982149</v>
       </c>
       <c r="E62">
-        <v>-22.6496991860038</v>
+        <v>-36.11710464790097</v>
       </c>
       <c r="F62">
-        <v>-3.960789181689176</v>
+        <v>-5.745706387564786</v>
       </c>
       <c r="G62">
-        <v>-12.51097980394872</v>
+        <v>-20.31164805304327</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.720338011813817</v>
       </c>
       <c r="E63">
-        <v>-22.36762506854002</v>
+        <v>-35.70914800997198</v>
       </c>
       <c r="F63">
-        <v>-3.899573658989695</v>
+        <v>-5.689645795212926</v>
       </c>
       <c r="G63">
-        <v>-13.02880871611044</v>
+        <v>-20.75564021276985</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.67404356570909</v>
       </c>
       <c r="E64">
-        <v>-23.40779290573186</v>
+        <v>-36.48417822248873</v>
       </c>
       <c r="F64">
-        <v>-3.783729791177795</v>
+        <v>-5.637277236375344</v>
       </c>
       <c r="G64">
-        <v>-12.29476145368784</v>
+        <v>-20.87388131252323</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.628192912644247</v>
       </c>
       <c r="E65">
-        <v>-22.91807014112037</v>
+        <v>-36.42599185996417</v>
       </c>
       <c r="F65">
-        <v>-3.838522981403372</v>
+        <v>-5.681638795897466</v>
       </c>
       <c r="G65">
-        <v>-12.84628509834826</v>
+        <v>-21.21062834950513</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.586312913632758</v>
       </c>
       <c r="E66">
-        <v>-22.42318038766612</v>
+        <v>-35.80376141741423</v>
       </c>
       <c r="F66">
-        <v>-3.937546849101427</v>
+        <v>-5.674553769501322</v>
       </c>
       <c r="G66">
-        <v>-12.37339684188214</v>
+        <v>-20.90583304279551</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.551620809493221</v>
       </c>
       <c r="E67">
-        <v>-22.2880869510693</v>
+        <v>-35.14601415322213</v>
       </c>
       <c r="F67">
-        <v>-3.818382056371704</v>
+        <v>-5.738372022580399</v>
       </c>
       <c r="G67">
-        <v>-12.80068895463588</v>
+        <v>-20.96910584441483</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.528780157974739</v>
       </c>
       <c r="E68">
-        <v>-22.24656084441896</v>
+        <v>-35.41794448890873</v>
       </c>
       <c r="F68">
-        <v>-3.757861533923172</v>
+        <v>-5.82649374689021</v>
       </c>
       <c r="G68">
-        <v>-12.58597690259537</v>
+        <v>-21.01737028783186</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.522129505316363</v>
       </c>
       <c r="E69">
-        <v>-22.1471019697885</v>
+        <v>-36.28283773963369</v>
       </c>
       <c r="F69">
-        <v>-3.977163520140313</v>
+        <v>-5.69837595927103</v>
       </c>
       <c r="G69">
-        <v>-12.73835800322248</v>
+        <v>-20.75580739531959</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.534670904009034</v>
       </c>
       <c r="E70">
-        <v>-22.85573116793078</v>
+        <v>-35.48960079736911</v>
       </c>
       <c r="F70">
-        <v>-3.855110210277029</v>
+        <v>-5.763409427330013</v>
       </c>
       <c r="G70">
-        <v>-12.63011971681601</v>
+        <v>-20.55377969851279</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.567931261563347</v>
       </c>
       <c r="E71">
-        <v>-22.65613867604271</v>
+        <v>-35.49155936237742</v>
       </c>
       <c r="F71">
-        <v>-4.008198304886197</v>
+        <v>-6.244060500762996</v>
       </c>
       <c r="G71">
-        <v>-12.49365902968725</v>
+        <v>-20.50309359103378</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.623577423527713</v>
       </c>
       <c r="E72">
-        <v>-23.33451313933974</v>
+        <v>-36.03196933655677</v>
       </c>
       <c r="F72">
-        <v>-4.184661270867561</v>
+        <v>-5.805985855099102</v>
       </c>
       <c r="G72">
-        <v>-12.62763680766155</v>
+        <v>-20.3917483576387</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.700788496225035</v>
       </c>
       <c r="E73">
-        <v>-22.98689388908894</v>
+        <v>-36.27841568476521</v>
       </c>
       <c r="F73">
-        <v>-4.301232445259119</v>
+        <v>-6.095268319504746</v>
       </c>
       <c r="G73">
-        <v>-12.66726734831217</v>
+        <v>-21.07990483779593</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.797022452925392</v>
       </c>
       <c r="E74">
-        <v>-23.55575173698448</v>
+        <v>-35.69935065645638</v>
       </c>
       <c r="F74">
-        <v>-4.38441544311344</v>
+        <v>-5.89521013642204</v>
       </c>
       <c r="G74">
-        <v>-11.97800514594483</v>
+        <v>-19.8946881529176</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.907361769460179</v>
       </c>
       <c r="E75">
-        <v>-23.44995752721728</v>
+        <v>-36.07125384857331</v>
       </c>
       <c r="F75">
-        <v>-4.385593381560221</v>
+        <v>-5.878452263863406</v>
       </c>
       <c r="G75">
-        <v>-12.72263953300202</v>
+        <v>-20.54295586987215</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.027280066648184</v>
       </c>
       <c r="E76">
-        <v>-23.48599512337032</v>
+        <v>-36.37231132907725</v>
       </c>
       <c r="F76">
-        <v>-4.449342051777463</v>
+        <v>-6.053269263815408</v>
       </c>
       <c r="G76">
-        <v>-11.62849099009073</v>
+        <v>-19.74866495499866</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.150361080277498</v>
       </c>
       <c r="E77">
-        <v>-23.47485960578546</v>
+        <v>-36.49883915708856</v>
       </c>
       <c r="F77">
-        <v>-4.327698783778564</v>
+        <v>-6.206144468002057</v>
       </c>
       <c r="G77">
-        <v>-12.10632189104698</v>
+        <v>-20.36773200502406</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.268862915732296</v>
       </c>
       <c r="E78">
-        <v>-23.74191730343981</v>
+        <v>-37.13182472540672</v>
       </c>
       <c r="F78">
-        <v>-4.826203659844084</v>
+        <v>-5.959379617279904</v>
       </c>
       <c r="G78">
-        <v>-11.96629243582689</v>
+        <v>-20.22801374108466</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.376108968251343</v>
       </c>
       <c r="E79">
-        <v>-24.84330105226734</v>
+        <v>-36.35426762439369</v>
       </c>
       <c r="F79">
-        <v>-4.634231170980104</v>
+        <v>-5.999919089605509</v>
       </c>
       <c r="G79">
-        <v>-12.37316179314886</v>
+        <v>-19.98748771020168</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.467051392096318</v>
       </c>
       <c r="E80">
-        <v>-25.24062483322633</v>
+        <v>-36.47389858649132</v>
       </c>
       <c r="F80">
-        <v>-4.520735724755141</v>
+        <v>-6.192927866090391</v>
       </c>
       <c r="G80">
-        <v>-11.80725051757476</v>
+        <v>-20.23712436240873</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.537092905546472</v>
       </c>
       <c r="E81">
-        <v>-24.65576335818768</v>
+        <v>-37.00046954410323</v>
       </c>
       <c r="F81">
-        <v>-4.657402263971211</v>
+        <v>-6.460334804122905</v>
       </c>
       <c r="G81">
-        <v>-11.47608340509931</v>
+        <v>-20.28066465734123</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.583091682367622</v>
       </c>
       <c r="E82">
-        <v>-25.34417291988571</v>
+        <v>-37.58356038580487</v>
       </c>
       <c r="F82">
-        <v>-4.404147983015528</v>
+        <v>-6.37859150881465</v>
       </c>
       <c r="G82">
-        <v>-11.96446170414367</v>
+        <v>-19.76231930007538</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.602531097400409</v>
       </c>
       <c r="E83">
-        <v>-26.83426729210965</v>
+        <v>-38.31681089712685</v>
       </c>
       <c r="F83">
-        <v>-4.604213621404858</v>
+        <v>-6.782606171977636</v>
       </c>
       <c r="G83">
-        <v>-11.57162905990821</v>
+        <v>-20.10403381063895</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.596161061175552</v>
       </c>
       <c r="E84">
-        <v>-27.27015102924395</v>
+        <v>-38.20177860038401</v>
       </c>
       <c r="F84">
-        <v>-4.747681885365316</v>
+        <v>-6.382097159663298</v>
       </c>
       <c r="G84">
-        <v>-11.31185386198714</v>
+        <v>-20.02247852127901</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.56510876695054</v>
       </c>
       <c r="E85">
-        <v>-27.55709325626598</v>
+        <v>-39.71111445866653</v>
       </c>
       <c r="F85">
-        <v>-4.730640711154924</v>
+        <v>-6.408484389095774</v>
       </c>
       <c r="G85">
-        <v>-11.26707211247742</v>
+        <v>-19.94885033321285</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.511032032460909</v>
       </c>
       <c r="E86">
-        <v>-29.30955835554631</v>
+        <v>-39.25335819207518</v>
       </c>
       <c r="F86">
-        <v>-4.797718589964017</v>
+        <v>-6.674567596018615</v>
       </c>
       <c r="G86">
-        <v>-11.21067034812486</v>
+        <v>-19.74871957900006</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.438032752711288</v>
       </c>
       <c r="E87">
-        <v>-29.47192226261732</v>
+        <v>-40.14602910236319</v>
       </c>
       <c r="F87">
-        <v>-5.096991993614825</v>
+        <v>-6.659466872449281</v>
       </c>
       <c r="G87">
-        <v>-11.57465820907665</v>
+        <v>-20.20056600801856</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.351015574344664</v>
       </c>
       <c r="E88">
-        <v>-31.0287550205293</v>
+        <v>-40.71726892758677</v>
       </c>
       <c r="F88">
-        <v>-4.954481322372004</v>
+        <v>-6.29610433957868</v>
       </c>
       <c r="G88">
-        <v>-11.52450344415669</v>
+        <v>-19.1728683904443</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.255324404386581</v>
       </c>
       <c r="E89">
-        <v>-30.62270260592052</v>
+        <v>-41.85642467811227</v>
       </c>
       <c r="F89">
-        <v>-4.989498069223145</v>
+        <v>-6.596213565938913</v>
       </c>
       <c r="G89">
-        <v>-11.30233935410728</v>
+        <v>-19.82918404360481</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.156256846266527</v>
       </c>
       <c r="E90">
-        <v>-32.39706061279094</v>
+        <v>-42.40795205598045</v>
       </c>
       <c r="F90">
-        <v>-5.082835194700982</v>
+        <v>-6.935094114403475</v>
       </c>
       <c r="G90">
-        <v>-11.04757301158712</v>
+        <v>-19.52880997046289</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.059724036452654</v>
       </c>
       <c r="E91">
-        <v>-33.34515551645883</v>
+        <v>-43.83496252104053</v>
       </c>
       <c r="F91">
-        <v>-5.176139185482707</v>
+        <v>-6.705104531955415</v>
       </c>
       <c r="G91">
-        <v>-11.62077079789315</v>
+        <v>-19.70034588758022</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.973169223199866</v>
       </c>
       <c r="E92">
-        <v>-34.82409399296487</v>
+        <v>-44.70603940302296</v>
       </c>
       <c r="F92">
-        <v>-5.368710583978911</v>
+        <v>-6.689828194496688</v>
       </c>
       <c r="G92">
-        <v>-11.27827499858232</v>
+        <v>-20.13397769504166</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.903349732252201</v>
       </c>
       <c r="E93">
-        <v>-36.10481663368116</v>
+        <v>-44.53637786008859</v>
       </c>
       <c r="F93">
-        <v>-5.385395560206098</v>
+        <v>-7.195329047462551</v>
       </c>
       <c r="G93">
-        <v>-12.2373168674904</v>
+        <v>-20.037524950755</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.855318718914646</v>
       </c>
       <c r="E94">
-        <v>-37.42486454268007</v>
+        <v>-45.01813277468359</v>
       </c>
       <c r="F94">
-        <v>-5.646575660471768</v>
+        <v>-7.002644576815865</v>
       </c>
       <c r="G94">
-        <v>-12.03571126523986</v>
+        <v>-20.57269781099696</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.83560267204822</v>
       </c>
       <c r="E95">
-        <v>-38.87722314099808</v>
+        <v>-46.29453072272256</v>
       </c>
       <c r="F95">
-        <v>-5.695832042977033</v>
+        <v>-7.074087123470309</v>
       </c>
       <c r="G95">
-        <v>-11.98960529751444</v>
+        <v>-19.54105567841265</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.850369418318971</v>
       </c>
       <c r="E96">
-        <v>-40.74253328407556</v>
+        <v>-48.87155848321555</v>
       </c>
       <c r="F96">
-        <v>-5.601574601314685</v>
+        <v>-7.123734909573396</v>
       </c>
       <c r="G96">
-        <v>-11.73956310347882</v>
+        <v>-20.22011974524627</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.900580336312981</v>
       </c>
       <c r="E97">
-        <v>-42.48610898887883</v>
+        <v>-49.19761880083433</v>
       </c>
       <c r="F97">
-        <v>-5.643364080051115</v>
+        <v>-7.10837614955809</v>
       </c>
       <c r="G97">
-        <v>-12.95632763207363</v>
+        <v>-20.6592305055752</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.991304501579351</v>
       </c>
       <c r="E98">
-        <v>-44.37039117381144</v>
+        <v>-50.97787627721824</v>
       </c>
       <c r="F98">
-        <v>-5.777678055843235</v>
+        <v>-7.0651188037839</v>
       </c>
       <c r="G98">
-        <v>-12.84966847588939</v>
+        <v>-20.92435554508773</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.116990719625317</v>
       </c>
       <c r="E99">
-        <v>-45.79643933814489</v>
+        <v>-51.78925881483157</v>
       </c>
       <c r="F99">
-        <v>-5.918157570214392</v>
+        <v>-7.035868736607348</v>
       </c>
       <c r="G99">
-        <v>-12.6854786593237</v>
+        <v>-20.98316573132011</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.286792217955194</v>
       </c>
       <c r="E100">
-        <v>-47.95573348532632</v>
+        <v>-52.84085199194476</v>
       </c>
       <c r="F100">
-        <v>-6.090994772073703</v>
+        <v>-7.710885452330998</v>
       </c>
       <c r="G100">
-        <v>-13.47957921782868</v>
+        <v>-21.27043169939929</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.482022164122231</v>
       </c>
       <c r="E101">
-        <v>-49.83690574073416</v>
+        <v>-54.73783428223188</v>
       </c>
       <c r="F101">
-        <v>-6.258565628169717</v>
+        <v>-7.47385723206135</v>
       </c>
       <c r="G101">
-        <v>-13.8814579277502</v>
+        <v>-21.47109710671668</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.724011505718003</v>
       </c>
       <c r="E102">
-        <v>-52.3061603483186</v>
+        <v>-56.34972988772162</v>
       </c>
       <c r="F102">
-        <v>-6.362196875362144</v>
+        <v>-7.525963198432245</v>
       </c>
       <c r="G102">
-        <v>-13.89782195435081</v>
+        <v>-21.76995660527438</v>
       </c>
     </row>
   </sheetData>
